--- a/data/trans_bre/P59A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,65</t>
+          <t>0,55; 7,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,52</t>
+          <t>-0,91; 7,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,31</t>
+          <t>2,62; 11,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,84</t>
+          <t>-2,42; 8,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 174,11</t>
+          <t>6,45; 190,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 122,66</t>
+          <t>-10,01; 126,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,8; 238,6</t>
+          <t>31,27; 232,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 361,22</t>
+          <t>-38,28; 371,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 11,23</t>
+          <t>-2,75; 11,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 15,21</t>
+          <t>1,29; 15,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 5,26</t>
+          <t>-8,24; 5,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 4,38</t>
+          <t>-21,32; 3,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 53,83</t>
+          <t>-10,87; 55,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 75,33</t>
+          <t>5,48; 75,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 17,63</t>
+          <t>-23,42; 19,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 15,81</t>
+          <t>-58,27; 14,15</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 8,76</t>
+          <t>-7,4; 9,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 20,46</t>
+          <t>-2,69; 20,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 10,88</t>
+          <t>-6,84; 10,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 11,88</t>
+          <t>-5,23; 11,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 121,38</t>
+          <t>-49,79; 129,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 115,91</t>
+          <t>-10,11; 124,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 54,21</t>
+          <t>-23,32; 52,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 48,46</t>
+          <t>-16,21; 50,71</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,2; -8,98</t>
+          <t>-26,71; -8,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,99; -0,64</t>
+          <t>-18,87; -1,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 4,4</t>
+          <t>-9,86; 4,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 11,01</t>
+          <t>-1,04; 10,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -61,84</t>
+          <t>-100,0; -58,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,97; -0,12</t>
+          <t>-81,47; -6,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 48,92</t>
+          <t>-61,03; 50,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 119,3</t>
+          <t>-7,68; 126,38</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -1,58</t>
+          <t>-21,5; -1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 9,92</t>
+          <t>-13,07; 9,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,58; -2,79</t>
+          <t>-20,3; -3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 0,31</t>
+          <t>-10,9; 0,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,86</t>
+          <t>-100,0; 24,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 218,65</t>
+          <t>-67,56; 195,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-88,35; -20,72</t>
+          <t>-87,82; -25,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 4,27</t>
+          <t>-65,66; 2,47</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 0,0</t>
+          <t>-12,81; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 2,43</t>
+          <t>-11,2; 2,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -2,49</t>
+          <t>-14,4; -2,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,87; -1,42</t>
+          <t>-10,3; -1,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,16; -21,53</t>
+          <t>-88,37; -26,31</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 0,0</t>
+          <t>-8,7; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 0,87</t>
+          <t>-6,8; 0,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,79; -2,71</t>
+          <t>-11,27; -2,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-97,79; -69,34</t>
+          <t>-97,69; -69,81</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,97</t>
+          <t>-6,08; -0,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,92</t>
+          <t>-3,79; 1,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,77</t>
+          <t>-6,25; -0,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,06</t>
+          <t>-5,78; 0,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -7,94</t>
+          <t>-40,28; -6,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 14,41</t>
+          <t>-22,49; 13,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,18; -4,5</t>
+          <t>-33,24; -5,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -0,59</t>
+          <t>-32,82; 0,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P59A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 7,7</t>
+          <t>0,51; 7,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,51</t>
+          <t>-0,21; 7,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 11,51</t>
+          <t>2,87; 11,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,85</t>
+          <t>-3,21; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 190,1</t>
+          <t>5,42; 193,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 126,7</t>
+          <t>-3,88; 126,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,27; 232,01</t>
+          <t>35,89; 241,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 371,56</t>
+          <t>-47,44; 225,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,92</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-19,47%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,79</t>
+          <t>-3,81; 9,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 15,31</t>
+          <t>0,54; 14,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 5,53</t>
+          <t>-9,08; 5,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 3,78</t>
+          <t>-6,48; 10,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 55,62</t>
+          <t>-14,36; 45,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 75,99</t>
+          <t>1,97; 70,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 19,48</t>
+          <t>-24,33; 19,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 14,15</t>
+          <t>-19,67; 44,84</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 9,68</t>
+          <t>-7,71; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 20,35</t>
+          <t>-2,65; 20,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 10,69</t>
+          <t>-6,63; 12,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 11,99</t>
+          <t>-5,52; 10,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 129,79</t>
+          <t>-51,13; 128,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 124,24</t>
+          <t>-9,66; 115,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 52,4</t>
+          <t>-23,36; 61,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 50,71</t>
+          <t>-15,89; 40,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,71; -8,42</t>
+          <t>-26,94; -8,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -1,5</t>
+          <t>-19,26; -0,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 4,36</t>
+          <t>-9,28; 4,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 10,59</t>
+          <t>0,02; 11,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -58,51</t>
+          <t>-100,0; -55,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,47; -6,63</t>
+          <t>-81,42; 5,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 50,86</t>
+          <t>-58,5; 51,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 126,38</t>
+          <t>-1,27; 128,53</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-38,55%</t>
+          <t>-37,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,5; -1,45</t>
+          <t>-22,85; -2,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 9,86</t>
+          <t>-15,5; 7,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,3; -3,21</t>
+          <t>-21,36; -2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 0,17</t>
+          <t>-10,41; 0,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,96</t>
+          <t>-95,27; -1,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 195,28</t>
+          <t>-72,09; 137,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-87,82; -25,36</t>
+          <t>-90,6; -16,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 2,47</t>
+          <t>-63,72; 6,82</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,3</t>
+          <t>-6,74</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-68,53%</t>
+          <t>-73,93%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 0,0</t>
+          <t>-9,83; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 2,59</t>
+          <t>-11,02; 2,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -2,47</t>
+          <t>-14,12; -2,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -1,41</t>
+          <t>-11,79; -2,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,37; -26,31</t>
+          <t>-90,0; -37,97</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,08</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-90,85%</t>
+          <t>-88,8%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,0</t>
+          <t>-8,39; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 0,87</t>
+          <t>-6,67; 0,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,27; -2,79</t>
+          <t>-11,1; -2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-97,69; -69,81</t>
+          <t>-96,63; -58,55</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-17,61%</t>
+          <t>-15,55%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,73</t>
+          <t>-6,01; -0,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,88</t>
+          <t>-3,86; 2,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,79</t>
+          <t>-6,09; -0,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,05</t>
+          <t>-5,1; 0,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -6,54</t>
+          <t>-39,84; -6,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 13,25</t>
+          <t>-23,19; 15,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -5,1</t>
+          <t>-32,59; -4,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 0,95</t>
+          <t>-28,53; 2,49</t>
         </is>
       </c>
     </row>
